--- a/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Patient</t>
   </si>
   <si>
     <t>ID</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">integer
 </t>
   </si>
   <si>
@@ -665,7 +665,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-patient-age-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
